--- a/dataset/clean/events-list.xlsx
+++ b/dataset/clean/events-list.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e3e6a90a7d0137c2/Desktop/ds/eu-power-market-comparison/dataset/clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_F25DC773A252ABDACC10485D695E56CA5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEFD9201-573B-4425-A873-574924AC30BC}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_F25DC773A252ABDACC10485D695E56CA5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2454BB7-CBD6-4FD6-8E1E-17A8E55AB58F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="credits" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$10</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -150,11 +153,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -167,7 +169,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -189,6 +190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,14 +462,13 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="90.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="90.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
+    <col min="4" max="4" width="90.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -485,13 +489,13 @@
       <c r="A2" s="2">
         <v>44378</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -499,13 +503,13 @@
       <c r="A3" s="2">
         <v>44531</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,13 +517,13 @@
       <c r="A4" s="2">
         <v>44616</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -527,13 +531,13 @@
       <c r="A5" s="2">
         <v>44774</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -541,13 +545,13 @@
       <c r="A6" s="2">
         <v>44830</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -555,13 +559,13 @@
       <c r="A7" s="2">
         <v>45047</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -569,96 +573,97 @@
       <c r="A8" s="2">
         <v>45638</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>45839</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>12</v>
+        <v>46082</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>46204</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="9"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="9"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="9"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D17" s="9"/>
-      <c r="F17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D20" s="9"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
